--- a/backtest_runs/20260410_193731/by_symbol/786/786.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/786/786.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
         <v>-12297.05999999999</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>141222.22</v>
@@ -955,7 +955,7 @@
         <v>-11059.62000000002</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>130162.6</v>
@@ -1001,7 +1001,7 @@
         <v>-8765.199999999997</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>121397.4</v>
@@ -1323,7 +1323,7 @@
         <v>-16112.5</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>175432.28</v>
@@ -1369,7 +1369,7 @@
         <v>-14488.35999999999</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>160943.92</v>
@@ -1415,7 +1415,7 @@
         <v>-12915.78</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>148028.14</v>
@@ -1553,7 +1553,7 @@
         <v>-14230.56000000001</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>158494.82</v>
@@ -1599,7 +1599,7 @@
         <v>-12786.88</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>145707.94</v>
@@ -1645,7 +1645,7 @@
         <v>-11523.66</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>134184.28</v>
